--- a/Hand_edited_log/StudentsSolution.xlsx
+++ b/Hand_edited_log/StudentsSolution.xlsx
@@ -49,10 +49,10 @@
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>06-12-2025 22:03:52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06-12-2025 22:04:30</x:t>
+    <x:t>06-12-2025 22:31:53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06-12-2025 22:33:39</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>

--- a/Hand_edited_log/StudentsSolution.xlsx
+++ b/Hand_edited_log/StudentsSolution.xlsx
@@ -49,10 +49,10 @@
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>06-12-2025 22:31:53</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06-12-2025 22:33:39</x:t>
+    <x:t>06-12-2025 22:43:17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06-12-2025 22:45:19</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>

--- a/Hand_edited_log/StudentsSolution.xlsx
+++ b/Hand_edited_log/StudentsSolution.xlsx
@@ -49,10 +49,10 @@
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>06-12-2025 22:43:17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06-12-2025 22:45:19</x:t>
+    <x:t>06-12-2025 23:14:17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06-12-2025 23:16:07</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>

--- a/Hand_edited_log/StudentsSolution.xlsx
+++ b/Hand_edited_log/StudentsSolution.xlsx
@@ -43,54 +43,60 @@
     <x:t>AnhDThe187386</x:t>
   </x:si>
   <x:si>
-    <x:t>Failed</x:t>
+    <x:t>Success</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 06:20:19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 06:22:32</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>anlpvhe187047</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cuongnvhe181200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 06:22:15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungdvhe181404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungtdhe186461</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 06:22:22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duongnthe186310</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Not Run</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>06-12-2025 23:14:17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06-12-2025 23:16:07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>anlpvhe187047</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Not Run</x:t>
-  </x:si>
-  <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cuongnvhe181200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dungdvhe181404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dungtdhe186461</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duongnthe186310</x:t>
-  </x:si>
-  <x:si>
     <x:t>7</x:t>
   </x:si>
   <x:si>
@@ -971,6 +977,12 @@
   </x:si>
   <x:si>
     <x:t>vietddhe161942</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-12-07 06:22:32</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.53s</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1011,7 +1023,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
+        <x:fgColor rgb="FF90EE90"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -1364,7 +1376,7 @@
     <x:col min="6" max="7" width="18.567768" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:7" s="1" customFormat="1">
+    <x:row r="1" spans="1:9" s="1" customFormat="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1387,7 +1399,7 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:7">
+    <x:row r="2" spans="1:9" s="2" customFormat="1">
       <x:c r="A2" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1404,3506 +1416,3512 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
         <x:v>12</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="H2" s="2" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>322</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9">
+      <x:c r="A3" s="2" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" s="2" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="C3" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="D3" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F3" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G3" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:9">
+      <x:c r="A4" s="2" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="B4" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D4" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E4" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="0" t="s">
+      <x:c r="F4" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G4" s="2" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+    </x:row>
+    <x:row r="5" spans="1:9">
+      <x:c r="A5" s="2" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="B5" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
+      <x:c r="D5" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E5" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:7">
-      <x:c r="A5" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
+      <x:c r="F5" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G5" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:9">
+      <x:c r="A6" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
+      <x:c r="C6" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
+      <x:c r="D6" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E6" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:7">
-      <x:c r="A6" s="0" t="s">
+      <x:c r="F6" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G6" s="2" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+    </x:row>
+    <x:row r="7" spans="1:9">
+      <x:c r="A7" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:7">
-      <x:c r="A7" s="0" t="s">
+      <x:c r="B7" s="0" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>24</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:9">
       <x:c r="A8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:9">
       <x:c r="A9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:9">
       <x:c r="A10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:9">
       <x:c r="A11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:9">
       <x:c r="A12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:9">
       <x:c r="A13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:9">
       <x:c r="A14" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:9">
       <x:c r="A16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:9">
       <x:c r="A22" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:9">
       <x:c r="A30" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:9">
       <x:c r="A33" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F34" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G34" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:9">
+      <x:c r="A35" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E34" s="0" t="s">
+      <x:c r="D35" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F35" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G35" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:9">
+      <x:c r="A36" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G36" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:9">
+      <x:c r="A37" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G37" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:9">
+      <x:c r="A38" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G38" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:9">
+      <x:c r="A39" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G39" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:9">
+      <x:c r="A40" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:9">
+      <x:c r="A41" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:9">
+      <x:c r="A42" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G42" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:9">
+      <x:c r="A43" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F43" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G43" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:9">
+      <x:c r="A44" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F44" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G44" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:9">
+      <x:c r="A45" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:9">
+      <x:c r="A46" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F46" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G46" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:9">
+      <x:c r="A47" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F47" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G47" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:9">
+      <x:c r="A48" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F48" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G48" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:9">
+      <x:c r="A49" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F49" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G49" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:9">
+      <x:c r="A50" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E50" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F50" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G50" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:9">
+      <x:c r="A51" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E51" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F51" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G51" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:9">
+      <x:c r="A52" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E52" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F52" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G52" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:9">
+      <x:c r="A53" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E53" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F53" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G53" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:9">
+      <x:c r="A54" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E54" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F54" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G54" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:9">
+      <x:c r="A55" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E55" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F55" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G55" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:9">
+      <x:c r="A56" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D56" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E56" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F56" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G56" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:9">
+      <x:c r="A57" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E57" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F57" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G57" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:9">
+      <x:c r="A58" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E58" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F58" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G58" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:9">
+      <x:c r="A59" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E59" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F59" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G59" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:9">
+      <x:c r="A60" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F60" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G60" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:9">
+      <x:c r="A61" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E61" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F61" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G61" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:9">
+      <x:c r="A62" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E62" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F62" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G62" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:9">
+      <x:c r="A63" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E63" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F63" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G63" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:9">
+      <x:c r="A64" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D64" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E64" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F64" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G64" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:9">
+      <x:c r="A65" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E65" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F65" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G65" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:9">
+      <x:c r="A66" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E66" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F66" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G66" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:9">
+      <x:c r="A67" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D67" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E67" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F67" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G67" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:9">
+      <x:c r="A68" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E68" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F68" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G68" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:9">
+      <x:c r="A69" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E69" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F69" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G69" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:9">
+      <x:c r="A70" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E70" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F70" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G70" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:9">
+      <x:c r="A71" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E71" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F71" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G71" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:9">
+      <x:c r="A72" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E72" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F72" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G72" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:9">
+      <x:c r="A73" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E73" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F73" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G73" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:9">
+      <x:c r="A74" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E74" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F74" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G74" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:9">
+      <x:c r="A75" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E75" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F75" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G75" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:9">
+      <x:c r="A76" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="C76" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D76" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E76" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F76" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G76" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:9">
+      <x:c r="A77" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="C77" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D77" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E77" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F77" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G77" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:9">
+      <x:c r="A78" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="C78" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E78" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F78" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G78" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:9">
+      <x:c r="A79" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F34" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G34" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:7">
-      <x:c r="A35" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
+      <x:c r="D79" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E79" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F79" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G79" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:9">
+      <x:c r="A80" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F35" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G35" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:7">
-      <x:c r="A36" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D36" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E36" s="0" t="s">
+      <x:c r="D80" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E80" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F80" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G80" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:9">
+      <x:c r="A81" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F36" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G36" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:7">
-      <x:c r="A37" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E37" s="0" t="s">
+      <x:c r="D81" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E81" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F81" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G81" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:9">
+      <x:c r="A82" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F37" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G37" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:7">
-      <x:c r="A38" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E38" s="0" t="s">
+      <x:c r="D82" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E82" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F82" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G82" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:9">
+      <x:c r="A83" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F38" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G38" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:7">
-      <x:c r="A39" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E39" s="0" t="s">
+      <x:c r="D83" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E83" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F83" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G83" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:9">
+      <x:c r="A84" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F39" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G39" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:7">
-      <x:c r="A40" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E40" s="0" t="s">
+      <x:c r="D84" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E84" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F84" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G84" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:9">
+      <x:c r="A85" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F40" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G40" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:7">
-      <x:c r="A41" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E41" s="0" t="s">
+      <x:c r="D85" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E85" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F85" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G85" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:9">
+      <x:c r="A86" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F41" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G41" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:7">
-      <x:c r="A42" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D42" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E42" s="0" t="s">
+      <x:c r="D86" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E86" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F86" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G86" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:9">
+      <x:c r="A87" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F42" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G42" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:7">
-      <x:c r="A43" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
+      <x:c r="D87" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E87" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F87" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G87" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:9">
+      <x:c r="A88" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F43" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G43" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:7">
-      <x:c r="A44" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D44" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E44" s="0" t="s">
+      <x:c r="D88" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E88" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F88" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G88" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:9">
+      <x:c r="A89" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F44" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G44" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:7">
-      <x:c r="A45" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E45" s="0" t="s">
+      <x:c r="D89" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E89" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F89" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G89" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:9">
+      <x:c r="A90" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F45" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G45" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:7">
-      <x:c r="A46" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
+      <x:c r="D90" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E90" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F90" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G90" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:9">
+      <x:c r="A91" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F46" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G46" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:7">
-      <x:c r="A47" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D47" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E47" s="0" t="s">
+      <x:c r="D91" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E91" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F91" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G91" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:9">
+      <x:c r="A92" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="C92" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F47" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G47" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:7">
-      <x:c r="A48" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E48" s="0" t="s">
+      <x:c r="D92" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E92" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F92" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G92" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:9">
+      <x:c r="A93" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="C93" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F48" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G48" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:7">
-      <x:c r="A49" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D49" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E49" s="0" t="s">
+      <x:c r="D93" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E93" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F93" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G93" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:9">
+      <x:c r="A94" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F49" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G49" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:7">
-      <x:c r="A50" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D50" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E50" s="0" t="s">
+      <x:c r="D94" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E94" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F94" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G94" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:9">
+      <x:c r="A95" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F50" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G50" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:7">
-      <x:c r="A51" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D51" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E51" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F51" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G51" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:7">
-      <x:c r="A52" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="C52" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D52" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E52" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F52" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G52" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:7">
-      <x:c r="A53" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D53" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E53" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F53" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G53" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:7">
-      <x:c r="A54" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D54" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E54" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F54" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G54" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:7">
-      <x:c r="A55" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D55" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E55" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F55" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G55" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:7">
-      <x:c r="A56" s="0" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="C56" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D56" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E56" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F56" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G56" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:7">
-      <x:c r="A57" s="0" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D57" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E57" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F57" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G57" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:7">
-      <x:c r="A58" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="C58" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D58" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E58" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F58" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G58" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:7">
-      <x:c r="A59" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="C59" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D59" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E59" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F59" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G59" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:7">
-      <x:c r="A60" s="0" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C60" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D60" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E60" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F60" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G60" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:7">
-      <x:c r="A61" s="0" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="C61" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D61" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E61" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F61" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G61" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:7">
-      <x:c r="A62" s="0" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="C62" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D62" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E62" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F62" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G62" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:7">
-      <x:c r="A63" s="0" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="C63" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D63" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E63" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F63" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G63" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:7">
-      <x:c r="A64" s="0" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C64" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D64" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E64" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F64" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G64" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:7">
-      <x:c r="A65" s="0" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="C65" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D65" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E65" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F65" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G65" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:7">
-      <x:c r="A66" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C66" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D66" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E66" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F66" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G66" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:7">
-      <x:c r="A67" s="0" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="C67" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D67" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E67" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F67" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G67" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:7">
-      <x:c r="A68" s="0" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="B68" s="0" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="C68" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D68" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E68" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F68" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G68" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:7">
-      <x:c r="A69" s="0" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="B69" s="0" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="C69" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D69" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E69" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F69" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G69" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:7">
-      <x:c r="A70" s="0" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="C70" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D70" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E70" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F70" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G70" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:7">
-      <x:c r="A71" s="0" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D71" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E71" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F71" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G71" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" spans="1:7">
-      <x:c r="A72" s="0" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="C72" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D72" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E72" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F72" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G72" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:7">
-      <x:c r="A73" s="0" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="C73" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D73" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E73" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F73" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G73" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" spans="1:7">
-      <x:c r="A74" s="0" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="B74" s="0" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="C74" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D74" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E74" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F74" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G74" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:7">
-      <x:c r="A75" s="0" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="B75" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C75" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D75" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E75" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F75" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G75" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" spans="1:7">
-      <x:c r="A76" s="0" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="B76" s="0" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="C76" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D76" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E76" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F76" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G76" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" spans="1:7">
-      <x:c r="A77" s="0" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="B77" s="0" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="C77" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D77" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E77" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F77" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G77" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" spans="1:7">
-      <x:c r="A78" s="0" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="B78" s="0" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="C78" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D78" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E78" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F78" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G78" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" spans="1:7">
-      <x:c r="A79" s="0" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="B79" s="0" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="C79" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D79" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E79" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F79" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G79" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" spans="1:7">
-      <x:c r="A80" s="0" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="C80" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D80" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E80" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F80" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G80" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" spans="1:7">
-      <x:c r="A81" s="0" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="B81" s="0" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="C81" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D81" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E81" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F81" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G81" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" spans="1:7">
-      <x:c r="A82" s="0" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="B82" s="0" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="C82" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D82" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E82" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F82" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G82" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" spans="1:7">
-      <x:c r="A83" s="0" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="C83" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D83" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E83" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F83" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G83" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" spans="1:7">
-      <x:c r="A84" s="0" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="B84" s="0" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="C84" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D84" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E84" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F84" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G84" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" spans="1:7">
-      <x:c r="A85" s="0" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="C85" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D85" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E85" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F85" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G85" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" spans="1:7">
-      <x:c r="A86" s="0" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="B86" s="0" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="C86" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D86" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E86" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F86" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G86" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" spans="1:7">
-      <x:c r="A87" s="0" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="B87" s="0" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="C87" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D87" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E87" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F87" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G87" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" spans="1:7">
-      <x:c r="A88" s="0" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="B88" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="C88" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D88" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E88" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F88" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G88" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" spans="1:7">
-      <x:c r="A89" s="0" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="C89" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D89" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E89" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F89" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G89" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" spans="1:7">
-      <x:c r="A90" s="0" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="C90" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D90" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E90" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F90" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G90" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" spans="1:7">
-      <x:c r="A91" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="B91" s="0" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="C91" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D91" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E91" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F91" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G91" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:7">
-      <x:c r="A92" s="0" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="B92" s="0" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="C92" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D92" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E92" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F92" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G92" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" spans="1:7">
-      <x:c r="A93" s="0" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="B93" s="0" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="C93" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D93" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E93" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F93" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G93" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:7">
-      <x:c r="A94" s="0" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="B94" s="0" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="C94" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D94" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E94" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F94" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G94" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:7">
-      <x:c r="A95" s="0" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="B95" s="0" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="C95" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G95" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:9">
       <x:c r="A96" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G96" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:9">
       <x:c r="A97" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G97" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:9">
       <x:c r="A98" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G98" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:9">
       <x:c r="A99" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G99" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:9">
       <x:c r="A100" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G100" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:9">
       <x:c r="A101" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G101" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:9">
       <x:c r="A102" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G102" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:9">
       <x:c r="A103" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G103" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:9">
       <x:c r="A104" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G104" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:9">
       <x:c r="A105" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G105" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:9">
       <x:c r="A106" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G106" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:9">
       <x:c r="A107" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G107" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:9">
       <x:c r="A108" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G108" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:9">
       <x:c r="A109" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G109" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:9">
       <x:c r="A110" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G110" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:9">
       <x:c r="A111" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G111" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:9">
       <x:c r="A112" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G112" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:9">
       <x:c r="A113" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G113" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:9">
       <x:c r="A114" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G114" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:9">
       <x:c r="A115" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G115" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:9">
       <x:c r="A116" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G116" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:9">
       <x:c r="A117" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G117" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:9">
       <x:c r="A118" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G118" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:9">
       <x:c r="A119" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G119" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="120" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:9">
       <x:c r="A120" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G120" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="121" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:9">
       <x:c r="A121" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G121" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="122" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:9">
       <x:c r="A122" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G122" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:9">
       <x:c r="A123" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G123" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="124" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:9">
       <x:c r="A124" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G124" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="125" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:9">
       <x:c r="A125" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G125" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="126" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:9">
       <x:c r="A126" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G126" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="127" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:9">
       <x:c r="A127" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G127" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="128" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:9">
       <x:c r="A128" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G128" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="129" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:9">
       <x:c r="A129" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G129" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="130" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:9">
       <x:c r="A130" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G130" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="131" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:9">
       <x:c r="A131" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G131" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="132" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:9">
       <x:c r="A132" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G132" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="133" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:9">
       <x:c r="A133" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G133" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="134" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:9">
       <x:c r="A134" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G134" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="135" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:9">
       <x:c r="A135" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G135" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="136" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:9">
       <x:c r="A136" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G136" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="137" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:9">
       <x:c r="A137" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G137" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="138" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:9">
       <x:c r="A138" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G138" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="139" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:9">
       <x:c r="A139" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G139" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="140" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:9">
       <x:c r="A140" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G140" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="141" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:9">
       <x:c r="A141" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G141" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="142" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:9">
       <x:c r="A142" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G142" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="143" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:9">
       <x:c r="A143" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G143" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="144" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:9">
       <x:c r="A144" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G144" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="145" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:9">
       <x:c r="A145" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G145" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="146" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:9">
       <x:c r="A146" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G146" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="147" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:9">
       <x:c r="A147" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G147" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="148" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:9">
       <x:c r="A148" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G148" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="149" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:9">
       <x:c r="A149" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G149" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="150" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:9">
       <x:c r="A150" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G150" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="151" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:9">
       <x:c r="A151" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G151" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="152" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:9">
       <x:c r="A152" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G152" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="153" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:9">
       <x:c r="A153" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G153" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="154" spans="1:7">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:9">
       <x:c r="A154" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G154" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Hand_edited_log/StudentsSolution.xlsx
+++ b/Hand_edited_log/StudentsSolution.xlsx
@@ -49,10 +49,10 @@
     <x:t>5</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 06:20:19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 06:22:32</x:t>
+    <x:t>07-12-2025 12:59:03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 13:01:01</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -61,928 +61,1375 @@
     <x:t>anlpvhe187047</x:t>
   </x:si>
   <x:si>
+    <x:t>07-12-2025 13:01:17</x:t>
+  </x:si>
+  <x:si>
     <x:t>3</x:t>
   </x:si>
   <x:si>
     <x:t>cuongnvhe181200</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 06:22:15</x:t>
+    <x:t>07-12-2025 13:01:07</x:t>
   </x:si>
   <x:si>
     <x:t>4</x:t>
   </x:si>
   <x:si>
+    <x:t>ducnthe180869</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Failed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 12:59:32</x:t>
+  </x:si>
+  <x:si>
     <x:t>dungdvhe181404</x:t>
   </x:si>
   <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
     <x:t>dungtdhe186461</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 06:22:22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
+    <x:t>7</x:t>
   </x:si>
   <x:si>
     <x:t>duongnthe186310</x:t>
   </x:si>
   <x:si>
+    <x:t>07-12-2025 13:01:40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DuyCNHE187327</x:t>
+  </x:si>
+  <x:si>
     <x:t>Not Run</x:t>
   </x:si>
   <x:si>
-    <x:t>0</x:t>
-  </x:si>
-  <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DuyCNHE187327</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
+    <x:t>9</x:t>
   </x:si>
   <x:si>
     <x:t>duyldhe176352</x:t>
   </x:si>
   <x:si>
-    <x:t>9</x:t>
+    <x:t>10</x:t>
   </x:si>
   <x:si>
     <x:t>duynthe180374</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GiangPTHE171781</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
   </x:si>
   <x:si>
     <x:t>hieunqhe171297</x:t>
   </x:si>
   <x:si>
-    <x:t>11</x:t>
+    <x:t>13</x:t>
   </x:si>
   <x:si>
     <x:t>HoangHHHE182296</x:t>
   </x:si>
   <x:si>
-    <x:t>12</x:t>
+    <x:t>14</x:t>
   </x:si>
   <x:si>
     <x:t>hungpvahe180492</x:t>
   </x:si>
   <x:si>
-    <x:t>13</x:t>
+    <x:t>15</x:t>
   </x:si>
   <x:si>
     <x:t>KienTTHE186727</x:t>
   </x:si>
   <x:si>
-    <x:t>14</x:t>
+    <x:t>16</x:t>
   </x:si>
   <x:si>
     <x:t>linhmndhe186854</x:t>
   </x:si>
   <x:si>
-    <x:t>15</x:t>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>linhndhe172819</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LongNBHE186897</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
   </x:si>
   <x:si>
     <x:t>manhcdhe176818</x:t>
   </x:si>
   <x:si>
-    <x:t>16</x:t>
+    <x:t>20</x:t>
   </x:si>
   <x:si>
     <x:t>MinhLAHE180101</x:t>
   </x:si>
   <x:si>
-    <x:t>17</x:t>
+    <x:t>21</x:t>
   </x:si>
   <x:si>
     <x:t>nguyendvhe176752</x:t>
   </x:si>
   <x:si>
-    <x:t>18</x:t>
+    <x:t>22</x:t>
   </x:si>
   <x:si>
     <x:t>nhandndhe180152</x:t>
   </x:si>
   <x:si>
-    <x:t>19</x:t>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sonnvhhe182275</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tainhhe181471</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tungbdhe172875</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
   </x:si>
   <x:si>
     <x:t>anhnhhe172209</x:t>
   </x:si>
   <x:si>
-    <x:t>20</x:t>
+    <x:t>27</x:t>
   </x:si>
   <x:si>
     <x:t>cuonghdhe173022</x:t>
   </x:si>
   <x:si>
-    <x:t>21</x:t>
+    <x:t>28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cuongnmhe182472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ducnthe160854</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungnmhe187141</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>halvhe182299</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32</x:t>
   </x:si>
   <x:si>
     <x:t>hieudmhe182298</x:t>
   </x:si>
   <x:si>
-    <x:t>22</x:t>
+    <x:t>33</x:t>
   </x:si>
   <x:si>
     <x:t>hieudnhe186375</x:t>
   </x:si>
   <x:si>
-    <x:t>23</x:t>
+    <x:t>34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hoangpvhe189009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huynqhe180360</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huynqhe181101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37</x:t>
   </x:si>
   <x:si>
     <x:t>KhaiTTHE180455</x:t>
   </x:si>
   <x:si>
-    <x:t>24</x:t>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kiennthe180530</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39</x:t>
   </x:si>
   <x:si>
     <x:t>lamtthe161932</x:t>
   </x:si>
   <x:si>
-    <x:t>25</x:t>
+    <x:t>40</x:t>
   </x:si>
   <x:si>
     <x:t>linhvhhe150945</x:t>
   </x:si>
   <x:si>
-    <x:t>26</x:t>
+    <x:t>41</x:t>
   </x:si>
   <x:si>
     <x:t>longtdhe186919</x:t>
   </x:si>
   <x:si>
-    <x:t>27</x:t>
+    <x:t>42</x:t>
   </x:si>
   <x:si>
     <x:t>luongndhe181876</x:t>
   </x:si>
   <x:si>
-    <x:t>28</x:t>
+    <x:t>43</x:t>
   </x:si>
   <x:si>
     <x:t>minhpdhe180520</x:t>
   </x:si>
   <x:si>
-    <x:t>29</x:t>
+    <x:t>44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>namlthe187066</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45</x:t>
   </x:si>
   <x:si>
     <x:t>Phienhdhe181642</x:t>
   </x:si>
   <x:si>
-    <x:t>30</x:t>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>quandxhe181250</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
   </x:si>
   <x:si>
     <x:t>QuanNDHE171155</x:t>
   </x:si>
   <x:si>
-    <x:t>31</x:t>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>quannmhe161255</x:t>
+  </x:si>
+  <x:si>
+    <x:t>49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thangdqhe180102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thanglmhe173199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thanhdhhe180714</x:t>
+  </x:si>
+  <x:si>
+    <x:t>52</x:t>
   </x:si>
   <x:si>
     <x:t>thanhnche171664</x:t>
   </x:si>
   <x:si>
-    <x:t>32</x:t>
+    <x:t>53</x:t>
   </x:si>
   <x:si>
     <x:t>tungbbhe176368</x:t>
   </x:si>
   <x:si>
-    <x:t>33</x:t>
+    <x:t>54</x:t>
   </x:si>
   <x:si>
     <x:t>tuyennvhe186728</x:t>
   </x:si>
   <x:si>
-    <x:t>34</x:t>
+    <x:t>55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>anhnvhe163786</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56</x:t>
   </x:si>
   <x:si>
     <x:t>anhptphe170125</x:t>
   </x:si>
   <x:si>
-    <x:t>35</x:t>
+    <x:t>57</x:t>
   </x:si>
   <x:si>
     <x:t>anhvqhe187074</x:t>
   </x:si>
   <x:si>
-    <x:t>36</x:t>
+    <x:t>58</x:t>
   </x:si>
   <x:si>
     <x:t>daipvhe161222</x:t>
   </x:si>
   <x:si>
-    <x:t>37</x:t>
+    <x:t>59</x:t>
   </x:si>
   <x:si>
     <x:t>datnthe187166</x:t>
   </x:si>
   <x:si>
-    <x:t>38</x:t>
+    <x:t>60</x:t>
   </x:si>
   <x:si>
     <x:t>dongnkhe172307</x:t>
   </x:si>
   <x:si>
-    <x:t>39</x:t>
+    <x:t>61</x:t>
   </x:si>
   <x:si>
     <x:t>dongtdhe171684</x:t>
   </x:si>
   <x:si>
-    <x:t>40</x:t>
+    <x:t>62</x:t>
   </x:si>
   <x:si>
     <x:t>ducnmhe182217</x:t>
   </x:si>
   <x:si>
-    <x:t>41</x:t>
+    <x:t>63</x:t>
   </x:si>
   <x:si>
     <x:t>dungpvhe180060</x:t>
   </x:si>
   <x:si>
-    <x:t>42</x:t>
+    <x:t>64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duongcqhe176062</x:t>
+  </x:si>
+  <x:si>
+    <x:t>65</x:t>
   </x:si>
   <x:si>
     <x:t>duynnhe176832</x:t>
   </x:si>
   <x:si>
-    <x:t>43</x:t>
+    <x:t>66</x:t>
   </x:si>
   <x:si>
     <x:t>hailvhe186288</x:t>
   </x:si>
   <x:si>
-    <x:t>44</x:t>
+    <x:t>67</x:t>
   </x:si>
   <x:si>
     <x:t>hieutmhe180724</x:t>
   </x:si>
   <x:si>
-    <x:t>45</x:t>
+    <x:t>68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hoangnlhe180286</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HoangNLHE186662</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70</x:t>
   </x:si>
   <x:si>
     <x:t>hungnvhe161335</x:t>
   </x:si>
   <x:si>
-    <x:t>46</x:t>
+    <x:t>71</x:t>
   </x:si>
   <x:si>
     <x:t>huynlhe172025</x:t>
   </x:si>
   <x:si>
-    <x:t>47</x:t>
+    <x:t>72</x:t>
   </x:si>
   <x:si>
     <x:t>kiemnvhe186025</x:t>
   </x:si>
   <x:si>
-    <x:t>48</x:t>
+    <x:t>73</x:t>
   </x:si>
   <x:si>
     <x:t>LinhPNHE180370</x:t>
   </x:si>
   <x:si>
-    <x:t>49</x:t>
+    <x:t>74</x:t>
   </x:si>
   <x:si>
     <x:t>sannxthe153321</x:t>
   </x:si>
   <x:si>
-    <x:t>50</x:t>
+    <x:t>75</x:t>
   </x:si>
   <x:si>
     <x:t>Sondphe182318</x:t>
   </x:si>
   <x:si>
-    <x:t>51</x:t>
+    <x:t>76</x:t>
   </x:si>
   <x:si>
     <x:t>tamtqhe181412</x:t>
   </x:si>
   <x:si>
-    <x:t>52</x:t>
+    <x:t>77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tanhmhe181126</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78</x:t>
   </x:si>
   <x:si>
     <x:t>tientvhe186986</x:t>
   </x:si>
   <x:si>
-    <x:t>53</x:t>
+    <x:t>79</x:t>
   </x:si>
   <x:si>
     <x:t>trinvmhe181736</x:t>
   </x:si>
   <x:si>
-    <x:t>54</x:t>
+    <x:t>80</x:t>
   </x:si>
   <x:si>
     <x:t>truonghnhe180891</x:t>
   </x:si>
   <x:si>
-    <x:t>55</x:t>
+    <x:t>81</x:t>
   </x:si>
   <x:si>
     <x:t>TuanTVHE181340</x:t>
   </x:si>
   <x:si>
-    <x:t>56</x:t>
+    <x:t>82</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tungnlhe186756</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83</x:t>
   </x:si>
   <x:si>
     <x:t>tungtthe173042</x:t>
   </x:si>
   <x:si>
-    <x:t>57</x:t>
+    <x:t>84</x:t>
   </x:si>
   <x:si>
     <x:t>anhndhe180067</x:t>
   </x:si>
   <x:si>
-    <x:t>58</x:t>
+    <x:t>85</x:t>
   </x:si>
   <x:si>
     <x:t>AnhNHHE180457</x:t>
   </x:si>
   <x:si>
-    <x:t>59</x:t>
+    <x:t>86</x:t>
   </x:si>
   <x:si>
     <x:t>anhnlhhe180328</x:t>
   </x:si>
   <x:si>
-    <x:t>60</x:t>
+    <x:t>87</x:t>
   </x:si>
   <x:si>
     <x:t>chientthe170152</x:t>
   </x:si>
   <x:si>
-    <x:t>61</x:t>
+    <x:t>88</x:t>
+  </x:si>
+  <x:si>
+    <x:t>chucvvhe150977</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89</x:t>
   </x:si>
   <x:si>
     <x:t>duchvhe181827</x:t>
   </x:si>
   <x:si>
-    <x:t>62</x:t>
+    <x:t>90</x:t>
   </x:si>
   <x:si>
     <x:t>ducmhhs173341</x:t>
   </x:si>
   <x:si>
-    <x:t>63</x:t>
+    <x:t>91</x:t>
   </x:si>
   <x:si>
     <x:t>dunghdhe153770</x:t>
   </x:si>
   <x:si>
-    <x:t>64</x:t>
+    <x:t>92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungnqhe186457</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungtmhe181358</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94</x:t>
   </x:si>
   <x:si>
     <x:t>duypqhe172390</x:t>
   </x:si>
   <x:si>
-    <x:t>65</x:t>
+    <x:t>95</x:t>
   </x:si>
   <x:si>
     <x:t>giangvthe187264</x:t>
   </x:si>
   <x:si>
-    <x:t>66</x:t>
+    <x:t>96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hailndhe182237</x:t>
+  </x:si>
+  <x:si>
+    <x:t>97</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hanhnxhe180944</x:t>
+  </x:si>
+  <x:si>
+    <x:t>98</x:t>
   </x:si>
   <x:si>
     <x:t>hoclhhe176114</x:t>
   </x:si>
   <x:si>
-    <x:t>67</x:t>
+    <x:t>99</x:t>
   </x:si>
   <x:si>
     <x:t>khanhnqhe173521</x:t>
   </x:si>
   <x:si>
-    <x:t>68</x:t>
+    <x:t>100</x:t>
   </x:si>
   <x:si>
     <x:t>namhdhe173231</x:t>
   </x:si>
   <x:si>
-    <x:t>69</x:t>
+    <x:t>101</x:t>
   </x:si>
   <x:si>
     <x:t>nhattmhe181227</x:t>
   </x:si>
   <x:si>
-    <x:t>70</x:t>
+    <x:t>102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>quanghvhe161464</x:t>
+  </x:si>
+  <x:si>
+    <x:t>103</x:t>
   </x:si>
   <x:si>
     <x:t>sonnhhe186392</x:t>
   </x:si>
   <x:si>
-    <x:t>71</x:t>
+    <x:t>104</x:t>
   </x:si>
   <x:si>
     <x:t>ThaoDPHE176894</x:t>
   </x:si>
   <x:si>
-    <x:t>72</x:t>
+    <x:t>105</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thaonthe151260</x:t>
+  </x:si>
+  <x:si>
+    <x:t>106</x:t>
   </x:si>
   <x:si>
     <x:t>thientdhe163943</x:t>
   </x:si>
   <x:si>
-    <x:t>73</x:t>
+    <x:t>107</x:t>
   </x:si>
   <x:si>
     <x:t>thinhndhe186687</x:t>
   </x:si>
   <x:si>
-    <x:t>74</x:t>
+    <x:t>108</x:t>
   </x:si>
   <x:si>
     <x:t>trapche186790</x:t>
   </x:si>
   <x:si>
-    <x:t>75</x:t>
+    <x:t>109</x:t>
   </x:si>
   <x:si>
     <x:t>truongdhhe187014</x:t>
   </x:si>
   <x:si>
-    <x:t>76</x:t>
+    <x:t>110</x:t>
+  </x:si>
+  <x:si>
+    <x:t>truongpqhe172222</x:t>
+  </x:si>
+  <x:si>
+    <x:t>111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>truongvxhe187103</x:t>
+  </x:si>
+  <x:si>
+    <x:t>112</x:t>
   </x:si>
   <x:si>
     <x:t>tuanvhhe182160</x:t>
   </x:si>
   <x:si>
-    <x:t>77</x:t>
+    <x:t>113</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tungdthe181764</x:t>
+  </x:si>
+  <x:si>
+    <x:t>114</x:t>
   </x:si>
   <x:si>
     <x:t>vietvhhe170993</x:t>
   </x:si>
   <x:si>
-    <x:t>78</x:t>
+    <x:t>115</x:t>
+  </x:si>
+  <x:si>
+    <x:t>anhdmhe181481</x:t>
+  </x:si>
+  <x:si>
+    <x:t>116</x:t>
+  </x:si>
+  <x:si>
+    <x:t>anhldhe180218</x:t>
+  </x:si>
+  <x:si>
+    <x:t>117</x:t>
   </x:si>
   <x:si>
     <x:t>anhndhe151333</x:t>
   </x:si>
   <x:si>
-    <x:t>79</x:t>
+    <x:t>118</x:t>
   </x:si>
   <x:si>
     <x:t>anhnvhe187352</x:t>
   </x:si>
   <x:si>
-    <x:t>80</x:t>
+    <x:t>119</x:t>
   </x:si>
   <x:si>
     <x:t>bacbxhe186736</x:t>
   </x:si>
   <x:si>
-    <x:t>81</x:t>
+    <x:t>120</x:t>
   </x:si>
   <x:si>
     <x:t>daitnahe181122</x:t>
   </x:si>
   <x:si>
-    <x:t>82</x:t>
+    <x:t>121</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dangvdhe180699</x:t>
+  </x:si>
+  <x:si>
+    <x:t>122</x:t>
   </x:si>
   <x:si>
     <x:t>ducndhe182000</x:t>
   </x:si>
   <x:si>
-    <x:t>83</x:t>
+    <x:t>123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ductnhe172615</x:t>
+  </x:si>
+  <x:si>
+    <x:t>124</x:t>
   </x:si>
   <x:si>
     <x:t>HaiLNHE181075</x:t>
   </x:si>
   <x:si>
-    <x:t>84</x:t>
+    <x:t>125</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hoadhhe186716</x:t>
+  </x:si>
+  <x:si>
+    <x:t>126</x:t>
   </x:si>
   <x:si>
     <x:t>hoangNVHE172566</x:t>
   </x:si>
   <x:si>
-    <x:t>85</x:t>
+    <x:t>127</x:t>
   </x:si>
   <x:si>
     <x:t>khanhtnhe180122</x:t>
   </x:si>
   <x:si>
-    <x:t>86</x:t>
+    <x:t>128</x:t>
   </x:si>
   <x:si>
     <x:t>khanhvdhe173081</x:t>
   </x:si>
   <x:si>
-    <x:t>87</x:t>
+    <x:t>129</x:t>
   </x:si>
   <x:si>
     <x:t>linhnthe170290</x:t>
   </x:si>
   <x:si>
-    <x:t>88</x:t>
+    <x:t>130</x:t>
   </x:si>
   <x:si>
     <x:t>minhndhe171146</x:t>
   </x:si>
   <x:si>
-    <x:t>89</x:t>
+    <x:t>131</x:t>
+  </x:si>
+  <x:si>
+    <x:t>minhpnhe187288</x:t>
+  </x:si>
+  <x:si>
+    <x:t>132</x:t>
   </x:si>
   <x:si>
     <x:t>namphhe181352</x:t>
   </x:si>
   <x:si>
-    <x:t>90</x:t>
+    <x:t>133</x:t>
+  </x:si>
+  <x:si>
+    <x:t>namphhe181666</x:t>
+  </x:si>
+  <x:si>
+    <x:t>134</x:t>
   </x:si>
   <x:si>
     <x:t>namVHHE180084</x:t>
   </x:si>
   <x:si>
-    <x:t>91</x:t>
+    <x:t>135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QuanNVHE186952</x:t>
+  </x:si>
+  <x:si>
+    <x:t>136</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sondthe171352</x:t>
+  </x:si>
+  <x:si>
+    <x:t>137</x:t>
   </x:si>
   <x:si>
     <x:t>thanhnths170500</x:t>
   </x:si>
   <x:si>
-    <x:t>92</x:t>
+    <x:t>138</x:t>
   </x:si>
   <x:si>
     <x:t>TrongLVHE173586</x:t>
   </x:si>
   <x:si>
-    <x:t>93</x:t>
+    <x:t>139</x:t>
   </x:si>
   <x:si>
     <x:t>TUANLQHE181759</x:t>
   </x:si>
   <x:si>
-    <x:t>94</x:t>
+    <x:t>140</x:t>
   </x:si>
   <x:si>
     <x:t>vuongnhhe186691</x:t>
   </x:si>
   <x:si>
-    <x:t>95</x:t>
+    <x:t>141</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AnhDHHE186569</x:t>
+  </x:si>
+  <x:si>
+    <x:t>142</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BangTCHE180772</x:t>
+  </x:si>
+  <x:si>
+    <x:t>143</x:t>
   </x:si>
   <x:si>
     <x:t>baonvthe180736</x:t>
   </x:si>
   <x:si>
-    <x:t>96</x:t>
+    <x:t>144</x:t>
   </x:si>
   <x:si>
     <x:t>datdthe181502</x:t>
   </x:si>
   <x:si>
-    <x:t>97</x:t>
+    <x:t>145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungtahe182204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>146</x:t>
   </x:si>
   <x:si>
     <x:t>duongnthe181806</x:t>
   </x:si>
   <x:si>
-    <x:t>98</x:t>
+    <x:t>147</x:t>
   </x:si>
   <x:si>
     <x:t>duyndhe180130</x:t>
   </x:si>
   <x:si>
-    <x:t>99</x:t>
+    <x:t>148</x:t>
   </x:si>
   <x:si>
     <x:t>hungpvhe180243</x:t>
   </x:si>
   <x:si>
-    <x:t>100</x:t>
+    <x:t>149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huylphe170368</x:t>
+  </x:si>
+  <x:si>
+    <x:t>150</x:t>
   </x:si>
   <x:si>
     <x:t>manhndhe186737</x:t>
   </x:si>
   <x:si>
-    <x:t>101</x:t>
+    <x:t>151</x:t>
   </x:si>
   <x:si>
     <x:t>namlxhhe186138</x:t>
   </x:si>
   <x:si>
-    <x:t>102</x:t>
+    <x:t>152</x:t>
   </x:si>
   <x:si>
     <x:t>namnhmhe171148</x:t>
   </x:si>
   <x:si>
-    <x:t>103</x:t>
+    <x:t>153</x:t>
   </x:si>
   <x:si>
     <x:t>phonglhhe186973</x:t>
   </x:si>
   <x:si>
-    <x:t>104</x:t>
+    <x:t>154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phongnhhe181714</x:t>
+  </x:si>
+  <x:si>
+    <x:t>155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PhuDKHE186439</x:t>
+  </x:si>
+  <x:si>
+    <x:t>156</x:t>
   </x:si>
   <x:si>
     <x:t>quannnhe176871</x:t>
   </x:si>
   <x:si>
-    <x:t>105</x:t>
+    <x:t>157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>quitdhe176583</x:t>
+  </x:si>
+  <x:si>
+    <x:t>158</x:t>
   </x:si>
   <x:si>
     <x:t>quyendvhe180585</x:t>
   </x:si>
   <x:si>
-    <x:t>106</x:t>
+    <x:t>159</x:t>
   </x:si>
   <x:si>
     <x:t>sonddthe173082</x:t>
   </x:si>
   <x:si>
-    <x:t>107</x:t>
+    <x:t>160</x:t>
   </x:si>
   <x:si>
     <x:t>tainvhe187366</x:t>
   </x:si>
   <x:si>
-    <x:t>108</x:t>
+    <x:t>161</x:t>
   </x:si>
   <x:si>
     <x:t>thainthe141476</x:t>
   </x:si>
   <x:si>
-    <x:t>109</x:t>
+    <x:t>162</x:t>
   </x:si>
   <x:si>
     <x:t>tientvhs176262</x:t>
   </x:si>
   <x:si>
-    <x:t>110</x:t>
+    <x:t>163</x:t>
   </x:si>
   <x:si>
     <x:t>tuannnhe151195</x:t>
   </x:si>
   <x:si>
-    <x:t>111</x:t>
+    <x:t>164</x:t>
   </x:si>
   <x:si>
     <x:t>tunahe186804</x:t>
   </x:si>
   <x:si>
-    <x:t>112</x:t>
+    <x:t>165</x:t>
   </x:si>
   <x:si>
     <x:t>Tungnxhe176893</x:t>
   </x:si>
   <x:si>
-    <x:t>113</x:t>
+    <x:t>166</x:t>
   </x:si>
   <x:si>
     <x:t>vietthhe186188</x:t>
   </x:si>
   <x:si>
-    <x:t>114</x:t>
+    <x:t>167</x:t>
   </x:si>
   <x:si>
     <x:t>anhtthhe181647</x:t>
   </x:si>
   <x:si>
-    <x:t>115</x:t>
+    <x:t>168</x:t>
   </x:si>
   <x:si>
     <x:t>ducnahe170599</x:t>
   </x:si>
   <x:si>
-    <x:t>116</x:t>
+    <x:t>169</x:t>
   </x:si>
   <x:si>
     <x:t>dungnmhe172726</x:t>
   </x:si>
   <x:si>
-    <x:t>117</x:t>
+    <x:t>170</x:t>
   </x:si>
   <x:si>
     <x:t>haidthe186882</x:t>
   </x:si>
   <x:si>
-    <x:t>118</x:t>
+    <x:t>171</x:t>
   </x:si>
   <x:si>
     <x:t>hienvmhe163953</x:t>
   </x:si>
   <x:si>
-    <x:t>119</x:t>
+    <x:t>172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hieplshe180170</x:t>
+  </x:si>
+  <x:si>
+    <x:t>173</x:t>
   </x:si>
   <x:si>
     <x:t>hieupmhe181979</x:t>
   </x:si>
   <x:si>
-    <x:t>120</x:t>
+    <x:t>174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hungcnthe170248</x:t>
+  </x:si>
+  <x:si>
+    <x:t>175</x:t>
   </x:si>
   <x:si>
     <x:t>HungNPHE186981</x:t>
   </x:si>
   <x:si>
-    <x:t>121</x:t>
+    <x:t>176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hungnthe172192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>177</x:t>
   </x:si>
   <x:si>
     <x:t>huynqhe171567</x:t>
   </x:si>
   <x:si>
-    <x:t>122</x:t>
+    <x:t>178</x:t>
   </x:si>
   <x:si>
     <x:t>huyvdhe173458</x:t>
   </x:si>
   <x:si>
-    <x:t>123</x:t>
+    <x:t>179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khanhnthe181027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>180</x:t>
   </x:si>
   <x:si>
     <x:t>kietpthe182092</x:t>
   </x:si>
   <x:si>
-    <x:t>124</x:t>
+    <x:t>181</x:t>
   </x:si>
   <x:si>
     <x:t>minhvqhe180094</x:t>
   </x:si>
   <x:si>
-    <x:t>125</x:t>
+    <x:t>182</x:t>
   </x:si>
   <x:si>
     <x:t>namnhhe161947</x:t>
   </x:si>
   <x:si>
-    <x:t>126</x:t>
+    <x:t>183</x:t>
   </x:si>
   <x:si>
     <x:t>nghianthe181360</x:t>
   </x:si>
   <x:si>
-    <x:t>127</x:t>
+    <x:t>184</x:t>
   </x:si>
   <x:si>
     <x:t>nguyenndhe186205</x:t>
   </x:si>
   <x:si>
-    <x:t>128</x:t>
+    <x:t>185</x:t>
   </x:si>
   <x:si>
     <x:t>QuanNAHE180983</x:t>
   </x:si>
   <x:si>
-    <x:t>129</x:t>
+    <x:t>186</x:t>
   </x:si>
   <x:si>
     <x:t>quocdkhe181519</x:t>
   </x:si>
   <x:si>
-    <x:t>130</x:t>
+    <x:t>187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sonthhe186811</x:t>
+  </x:si>
+  <x:si>
+    <x:t>188</x:t>
   </x:si>
   <x:si>
     <x:t>thangtdhe173186</x:t>
   </x:si>
   <x:si>
-    <x:t>131</x:t>
+    <x:t>189</x:t>
   </x:si>
   <x:si>
     <x:t>Tiennxhe181563</x:t>
   </x:si>
   <x:si>
-    <x:t>132</x:t>
+    <x:t>190</x:t>
   </x:si>
   <x:si>
     <x:t>tienpqhe176483</x:t>
   </x:si>
   <x:si>
-    <x:t>133</x:t>
+    <x:t>191</x:t>
   </x:si>
   <x:si>
     <x:t>tuanmahe182582</x:t>
   </x:si>
   <x:si>
-    <x:t>134</x:t>
+    <x:t>192</x:t>
   </x:si>
   <x:si>
     <x:t>tunpthe187324</x:t>
   </x:si>
   <x:si>
-    <x:t>135</x:t>
+    <x:t>193</x:t>
   </x:si>
   <x:si>
     <x:t>vannthe151384</x:t>
   </x:si>
   <x:si>
-    <x:t>136</x:t>
+    <x:t>194</x:t>
   </x:si>
   <x:si>
     <x:t>vinhnqhe187284</x:t>
   </x:si>
   <x:si>
-    <x:t>137</x:t>
+    <x:t>195</x:t>
   </x:si>
   <x:si>
     <x:t>vutnhe186197</x:t>
   </x:si>
   <x:si>
-    <x:t>138</x:t>
+    <x:t>196</x:t>
   </x:si>
   <x:si>
     <x:t>anhnnhe160896</x:t>
   </x:si>
   <x:si>
-    <x:t>139</x:t>
+    <x:t>197</x:t>
+  </x:si>
+  <x:si>
+    <x:t>baotkthe180715</x:t>
+  </x:si>
+  <x:si>
+    <x:t>198</x:t>
   </x:si>
   <x:si>
     <x:t>chiennvhe140896</x:t>
   </x:si>
   <x:si>
-    <x:t>140</x:t>
+    <x:t>199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>chinhndhe182189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cuongddhe187082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cuongnqhe163974</x:t>
+  </x:si>
+  <x:si>
+    <x:t>202</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAITQHE182481</x:t>
+  </x:si>
+  <x:si>
+    <x:t>203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>datmthe176706</x:t>
+  </x:si>
+  <x:si>
+    <x:t>204</x:t>
   </x:si>
   <x:si>
     <x:t>datnvhe180346</x:t>
   </x:si>
   <x:si>
-    <x:t>141</x:t>
+    <x:t>205</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ducnhhe182236</x:t>
+  </x:si>
+  <x:si>
+    <x:t>206</x:t>
+  </x:si>
+  <x:si>
+    <x:t>giangdhhe172332</x:t>
+  </x:si>
+  <x:si>
+    <x:t>207</x:t>
   </x:si>
   <x:si>
     <x:t>hanvhe172749</x:t>
   </x:si>
   <x:si>
-    <x:t>142</x:t>
+    <x:t>208</x:t>
   </x:si>
   <x:si>
     <x:t>hanvvhe180111</x:t>
   </x:si>
   <x:si>
-    <x:t>143</x:t>
+    <x:t>209</x:t>
   </x:si>
   <x:si>
     <x:t>haodnche176449</x:t>
   </x:si>
   <x:si>
-    <x:t>144</x:t>
+    <x:t>210</x:t>
   </x:si>
   <x:si>
     <x:t>Khaipghe186242</x:t>
   </x:si>
   <x:si>
-    <x:t>145</x:t>
+    <x:t>211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khoandhe182359</x:t>
+  </x:si>
+  <x:si>
+    <x:t>212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>loclvvhe180443</x:t>
+  </x:si>
+  <x:si>
+    <x:t>213</x:t>
   </x:si>
   <x:si>
     <x:t>luanndhe180066</x:t>
   </x:si>
   <x:si>
-    <x:t>146</x:t>
+    <x:t>214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>manhbche170750</x:t>
+  </x:si>
+  <x:si>
+    <x:t>215</x:t>
   </x:si>
   <x:si>
     <x:t>namnhhe186257</x:t>
   </x:si>
   <x:si>
-    <x:t>147</x:t>
+    <x:t>216</x:t>
+  </x:si>
+  <x:si>
+    <x:t>namntphe181708</x:t>
+  </x:si>
+  <x:si>
+    <x:t>217</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nampvhhe180065</x:t>
+  </x:si>
+  <x:si>
+    <x:t>218</x:t>
   </x:si>
   <x:si>
     <x:t>phonghthe170574</x:t>
   </x:si>
   <x:si>
-    <x:t>148</x:t>
+    <x:t>219</x:t>
   </x:si>
   <x:si>
     <x:t>thangtnhe186465</x:t>
   </x:si>
   <x:si>
-    <x:t>149</x:t>
+    <x:t>220</x:t>
   </x:si>
   <x:si>
     <x:t>thangvdhe189003</x:t>
   </x:si>
   <x:si>
-    <x:t>150</x:t>
+    <x:t>221</x:t>
   </x:si>
   <x:si>
     <x:t>toannqhe186921</x:t>
   </x:si>
   <x:si>
-    <x:t>151</x:t>
+    <x:t>222</x:t>
   </x:si>
   <x:si>
     <x:t>tuandmhe181577</x:t>
   </x:si>
   <x:si>
-    <x:t>152</x:t>
+    <x:t>223</x:t>
   </x:si>
   <x:si>
     <x:t>tuannahe181942</x:t>
   </x:si>
   <x:si>
-    <x:t>153</x:t>
+    <x:t>224</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TuanNDHE171613</x:t>
+  </x:si>
+  <x:si>
+    <x:t>225</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tunglahe187123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>226</x:t>
   </x:si>
   <x:si>
     <x:t>vietddhe161942</x:t>
   </x:si>
   <x:si>
-    <x:t>2025-12-07 06:22:32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.53s</x:t>
+    <x:t>2025-12-07 13:01:40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39.23s</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1009,7 +1456,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -1024,6 +1471,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -1046,7 +1498,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1056,8 +1508,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -1067,6 +1522,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1365,7 +1824,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G154"/>
+  <x:dimension ref="A1:G227"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="3.996339" style="0" customWidth="1"/>
@@ -1422,10 +1881,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>321</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>322</x:v>
+        <x:v>471</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -1448,15 +1907,15 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
       <x:c r="A4" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
         <x:v>7</x:v>
@@ -1471,30 +1930,30 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G4" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
-      <x:c r="A5" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B5" s="2" t="s">
+      <x:c r="A5" s="3" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C5" s="2" t="s">
+      <x:c r="B5" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D5" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E5" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F5" s="2" t="s">
+      <x:c r="D5" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E5" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F5" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G5" s="2" t="s">
-        <x:v>12</x:v>
+      <x:c r="G5" s="3" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -1502,7 +1961,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
         <x:v>7</x:v>
@@ -1517,3411 +1976,5090 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G6" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
-      <x:c r="A7" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="A7" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B7" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E7" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F7" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G7" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:9">
+      <x:c r="A8" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B8" s="2" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D8" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E8" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F8" s="2" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:9">
-      <x:c r="A8" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>26</x:v>
+      <x:c r="G8" s="2" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
       <x:c r="A9" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
       <x:c r="A10" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
       <x:c r="A11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
       <x:c r="A12" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
       <x:c r="A13" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
       <x:c r="A14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
       <x:c r="A16" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
       <x:c r="A22" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
       <x:c r="A30" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
       <x:c r="A33" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
       <x:c r="A36" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
       <x:c r="A37" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
       <x:c r="A38" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
       <x:c r="A39" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
       <x:c r="A40" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
       <x:c r="A41" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
       <x:c r="A42" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
       <x:c r="A43" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
       <x:c r="A44" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G44" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
       <x:c r="A45" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G45" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
       <x:c r="A46" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G46" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
       <x:c r="A47" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G47" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
       <x:c r="A48" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G48" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
       <x:c r="A49" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G49" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
       <x:c r="A50" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
       <x:c r="A51" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G51" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
       <x:c r="A52" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G52" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
       <x:c r="A53" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G53" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
       <x:c r="A54" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G54" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
       <x:c r="A55" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G55" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:9">
       <x:c r="A56" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G56" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:9">
       <x:c r="A57" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G57" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:9">
       <x:c r="A58" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G58" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:9">
       <x:c r="A59" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G59" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:9">
       <x:c r="A60" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G60" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:9">
       <x:c r="A61" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G61" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:9">
       <x:c r="A62" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G62" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:9">
       <x:c r="A63" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G63" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:9">
       <x:c r="A64" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G64" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:9">
       <x:c r="A65" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G65" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:9">
       <x:c r="A66" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G66" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:9">
       <x:c r="A67" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G67" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:9">
       <x:c r="A68" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G68" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:9">
       <x:c r="A69" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G69" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:9">
       <x:c r="A70" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G70" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:9">
       <x:c r="A71" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G71" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:9">
       <x:c r="A72" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G72" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:9">
       <x:c r="A73" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G73" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:9">
       <x:c r="A74" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G74" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:9">
       <x:c r="A75" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G75" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:9">
       <x:c r="A76" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G76" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:9">
       <x:c r="A77" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G77" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:9">
       <x:c r="A78" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G78" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:9">
       <x:c r="A79" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G79" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:9">
       <x:c r="A80" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G80" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:9">
       <x:c r="A81" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G81" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:9">
       <x:c r="A82" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G82" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:9">
       <x:c r="A83" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G83" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:9">
       <x:c r="A84" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G84" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:9">
       <x:c r="A85" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G85" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:9">
       <x:c r="A86" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G86" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:9">
       <x:c r="A87" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G87" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:9">
       <x:c r="A88" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G88" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:9">
       <x:c r="A89" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G89" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:9">
       <x:c r="A90" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G90" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:9">
       <x:c r="A91" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G91" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:9">
       <x:c r="A92" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G92" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:9">
       <x:c r="A93" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G93" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:9">
       <x:c r="A94" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G94" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:9">
       <x:c r="A95" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G95" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:9">
       <x:c r="A96" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G96" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:9">
       <x:c r="A97" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G97" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:9">
       <x:c r="A98" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G98" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:9">
       <x:c r="A99" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G99" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:9">
       <x:c r="A100" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G100" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:9">
       <x:c r="A101" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G101" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:9">
       <x:c r="A102" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G102" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:9">
       <x:c r="A103" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G103" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:9">
       <x:c r="A104" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G104" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:9">
       <x:c r="A105" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G105" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:9">
       <x:c r="A106" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G106" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:9">
       <x:c r="A107" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G107" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:9">
       <x:c r="A108" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G108" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:9">
       <x:c r="A109" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G109" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:9">
       <x:c r="A110" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G110" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:9">
       <x:c r="A111" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G111" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:9">
       <x:c r="A112" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G112" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:9">
       <x:c r="A113" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G113" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:9">
       <x:c r="A114" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G114" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:9">
       <x:c r="A115" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G115" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:9">
       <x:c r="A116" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G116" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:9">
       <x:c r="A117" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G117" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:9">
       <x:c r="A118" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G118" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:9">
       <x:c r="A119" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G119" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:9">
       <x:c r="A120" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G120" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:9">
       <x:c r="A121" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G121" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:9">
       <x:c r="A122" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G122" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:9">
       <x:c r="A123" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G123" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:9">
       <x:c r="A124" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G124" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:9">
       <x:c r="A125" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G125" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:9">
       <x:c r="A126" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G126" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:9">
       <x:c r="A127" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G127" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:9">
       <x:c r="A128" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G128" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:9">
       <x:c r="A129" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G129" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:9">
       <x:c r="A130" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G130" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:9">
       <x:c r="A131" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G131" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:9">
       <x:c r="A132" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G132" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:9">
       <x:c r="A133" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G133" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:9">
       <x:c r="A134" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G134" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:9">
       <x:c r="A135" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G135" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:9">
       <x:c r="A136" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G136" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:9">
       <x:c r="A137" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G137" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:9">
       <x:c r="A138" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G138" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:9">
       <x:c r="A139" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G139" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:9">
       <x:c r="A140" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G140" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:9">
       <x:c r="A141" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G141" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:9">
       <x:c r="A142" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G142" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:9">
       <x:c r="A143" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G143" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:9">
       <x:c r="A144" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G144" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:9">
       <x:c r="A145" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G145" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:9">
       <x:c r="A146" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G146" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:9">
       <x:c r="A147" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G147" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:9">
       <x:c r="A148" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G148" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:9">
       <x:c r="A149" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G149" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:9">
       <x:c r="A150" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G150" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:9">
       <x:c r="A151" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G151" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:9">
       <x:c r="A152" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G152" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:9">
       <x:c r="A153" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G153" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:9">
       <x:c r="A154" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F154" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G154" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:9">
+      <x:c r="A155" s="0" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="C155" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F154" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G154" s="0" t="s">
-        <x:v>26</x:v>
+      <x:c r="D155" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E155" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F155" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G155" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:9">
+      <x:c r="A156" s="0" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="C156" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D156" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E156" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F156" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G156" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:9">
+      <x:c r="A157" s="0" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D157" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E157" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F157" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G157" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:9">
+      <x:c r="A158" s="0" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D158" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E158" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F158" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G158" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:9">
+      <x:c r="A159" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="C159" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D159" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E159" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F159" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G159" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:9">
+      <x:c r="A160" s="0" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="C160" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D160" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E160" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F160" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G160" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:9">
+      <x:c r="A161" s="0" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D161" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E161" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F161" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G161" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:9">
+      <x:c r="A162" s="0" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="C162" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D162" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E162" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F162" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G162" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:9">
+      <x:c r="A163" s="0" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="B163" s="0" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="C163" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D163" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E163" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F163" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G163" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:9">
+      <x:c r="A164" s="0" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="C164" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D164" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E164" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F164" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G164" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:9">
+      <x:c r="A165" s="0" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="C165" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D165" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E165" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F165" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G165" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:9">
+      <x:c r="A166" s="0" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="C166" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D166" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E166" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F166" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G166" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:9">
+      <x:c r="A167" s="0" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="C167" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D167" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E167" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F167" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G167" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:9">
+      <x:c r="A168" s="0" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="C168" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D168" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E168" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F168" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G168" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:9">
+      <x:c r="A169" s="0" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="C169" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D169" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E169" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F169" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G169" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:9">
+      <x:c r="A170" s="0" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="C170" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D170" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E170" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F170" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G170" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:9">
+      <x:c r="A171" s="0" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="B171" s="0" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="C171" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D171" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E171" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F171" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G171" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:9">
+      <x:c r="A172" s="0" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="B172" s="0" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="C172" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D172" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E172" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F172" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G172" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:9">
+      <x:c r="A173" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="B173" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="C173" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D173" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E173" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F173" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G173" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:9">
+      <x:c r="A174" s="0" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="B174" s="0" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="C174" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D174" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E174" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F174" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G174" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:9">
+      <x:c r="A175" s="0" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="B175" s="0" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="C175" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D175" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E175" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F175" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G175" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:9">
+      <x:c r="A176" s="0" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="B176" s="0" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="C176" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D176" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E176" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F176" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G176" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:9">
+      <x:c r="A177" s="0" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="B177" s="0" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="C177" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D177" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E177" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F177" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G177" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:9">
+      <x:c r="A178" s="0" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B178" s="0" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="C178" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D178" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E178" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F178" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G178" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:9">
+      <x:c r="A179" s="0" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="B179" s="0" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="C179" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D179" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E179" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F179" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G179" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:9">
+      <x:c r="A180" s="0" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="B180" s="0" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="C180" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D180" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E180" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F180" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G180" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:9">
+      <x:c r="A181" s="0" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="B181" s="0" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="C181" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D181" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E181" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F181" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G181" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" spans="1:9">
+      <x:c r="A182" s="0" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="B182" s="0" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="C182" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D182" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E182" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F182" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G182" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:9">
+      <x:c r="A183" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="B183" s="0" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="C183" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D183" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E183" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F183" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G183" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:9">
+      <x:c r="A184" s="0" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="B184" s="0" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="C184" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D184" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E184" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F184" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G184" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:9">
+      <x:c r="A185" s="0" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="B185" s="0" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="C185" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D185" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E185" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F185" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G185" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:9">
+      <x:c r="A186" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="B186" s="0" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="C186" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D186" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E186" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F186" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G186" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:9">
+      <x:c r="A187" s="0" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B187" s="0" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="C187" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D187" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E187" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F187" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G187" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" spans="1:9">
+      <x:c r="A188" s="0" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="B188" s="0" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="C188" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D188" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E188" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F188" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G188" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:9">
+      <x:c r="A189" s="0" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="B189" s="0" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="C189" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D189" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E189" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F189" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G189" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:9">
+      <x:c r="A190" s="0" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="B190" s="0" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="C190" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D190" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E190" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F190" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G190" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:9">
+      <x:c r="A191" s="0" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="B191" s="0" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="C191" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D191" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E191" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F191" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G191" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:9">
+      <x:c r="A192" s="0" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="B192" s="0" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="C192" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D192" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E192" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F192" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G192" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:9">
+      <x:c r="A193" s="0" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="B193" s="0" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="C193" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D193" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E193" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F193" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G193" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:9">
+      <x:c r="A194" s="0" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="B194" s="0" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="C194" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D194" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E194" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F194" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G194" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:9">
+      <x:c r="A195" s="0" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="B195" s="0" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="C195" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D195" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E195" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F195" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G195" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:9">
+      <x:c r="A196" s="0" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="B196" s="0" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="C196" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D196" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E196" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F196" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G196" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:9">
+      <x:c r="A197" s="0" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="B197" s="0" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="C197" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D197" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E197" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F197" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G197" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:9">
+      <x:c r="A198" s="0" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="B198" s="0" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="C198" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D198" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E198" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F198" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G198" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" spans="1:9">
+      <x:c r="A199" s="0" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="B199" s="0" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="C199" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D199" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E199" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F199" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G199" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" spans="1:9">
+      <x:c r="A200" s="0" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="B200" s="0" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="C200" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D200" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E200" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F200" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G200" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" spans="1:9">
+      <x:c r="A201" s="0" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="B201" s="0" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="C201" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D201" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E201" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F201" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G201" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" spans="1:9">
+      <x:c r="A202" s="0" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="B202" s="0" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="C202" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D202" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E202" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F202" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G202" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" spans="1:9">
+      <x:c r="A203" s="0" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="B203" s="0" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="C203" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D203" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E203" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F203" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G203" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" spans="1:9">
+      <x:c r="A204" s="0" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="B204" s="0" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="C204" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D204" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E204" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F204" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G204" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" spans="1:9">
+      <x:c r="A205" s="0" t="s">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="B205" s="0" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="C205" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D205" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E205" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F205" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G205" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" spans="1:9">
+      <x:c r="A206" s="0" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="B206" s="0" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="C206" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D206" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E206" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F206" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G206" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" spans="1:9">
+      <x:c r="A207" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="B207" s="0" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="C207" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D207" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E207" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F207" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G207" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" spans="1:9">
+      <x:c r="A208" s="0" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="B208" s="0" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="C208" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D208" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E208" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F208" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G208" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" spans="1:9">
+      <x:c r="A209" s="0" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="B209" s="0" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="C209" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D209" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E209" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F209" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G209" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" spans="1:9">
+      <x:c r="A210" s="0" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="B210" s="0" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="C210" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D210" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E210" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F210" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G210" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" spans="1:9">
+      <x:c r="A211" s="0" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="B211" s="0" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="C211" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D211" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E211" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F211" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G211" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" spans="1:9">
+      <x:c r="A212" s="0" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="B212" s="0" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="C212" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D212" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E212" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F212" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G212" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" spans="1:9">
+      <x:c r="A213" s="0" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="B213" s="0" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="C213" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D213" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E213" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F213" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G213" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" spans="1:9">
+      <x:c r="A214" s="0" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="B214" s="0" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="C214" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D214" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E214" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F214" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G214" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" spans="1:9">
+      <x:c r="A215" s="0" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="B215" s="0" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="C215" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D215" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E215" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F215" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G215" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" spans="1:9">
+      <x:c r="A216" s="0" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="B216" s="0" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="C216" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D216" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E216" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F216" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G216" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" spans="1:9">
+      <x:c r="A217" s="0" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="B217" s="0" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="C217" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D217" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E217" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F217" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G217" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" spans="1:9">
+      <x:c r="A218" s="0" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="B218" s="0" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="C218" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D218" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E218" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F218" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G218" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" spans="1:9">
+      <x:c r="A219" s="0" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="B219" s="0" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="C219" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D219" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E219" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F219" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G219" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" spans="1:9">
+      <x:c r="A220" s="0" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="B220" s="0" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="C220" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D220" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E220" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F220" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G220" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" spans="1:9">
+      <x:c r="A221" s="0" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="B221" s="0" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="C221" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D221" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E221" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F221" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G221" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" spans="1:9">
+      <x:c r="A222" s="0" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="B222" s="0" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="C222" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D222" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E222" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F222" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G222" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" spans="1:9">
+      <x:c r="A223" s="0" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="B223" s="0" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="C223" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D223" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E223" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F223" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G223" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" spans="1:9">
+      <x:c r="A224" s="0" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="B224" s="0" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="C224" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D224" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E224" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F224" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G224" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" spans="1:9">
+      <x:c r="A225" s="0" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="B225" s="0" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="C225" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D225" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E225" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F225" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G225" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" spans="1:9">
+      <x:c r="A226" s="0" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="B226" s="0" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="C226" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D226" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E226" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F226" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G226" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" spans="1:9">
+      <x:c r="A227" s="0" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B227" s="0" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="C227" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D227" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E227" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F227" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G227" s="0" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Hand_edited_log/StudentsSolution.xlsx
+++ b/Hand_edited_log/StudentsSolution.xlsx
@@ -85,10 +85,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 16:29:56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 16:31:28</x:t>
+    <x:t>07-12-2025 16:41:43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 16:43:31</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>

--- a/Hand_edited_log/StudentsSolution.xlsx
+++ b/Hand_edited_log/StudentsSolution.xlsx
@@ -85,10 +85,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 16:41:43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 16:43:31</x:t>
+    <x:t>07-12-2025 17:26:23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 17:27:58</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>

--- a/Hand_edited_log/StudentsSolution.xlsx
+++ b/Hand_edited_log/StudentsSolution.xlsx
@@ -85,10 +85,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 17:26:23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 17:27:58</x:t>
+    <x:t>07-12-2025 17:45:16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 17:46:52</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>

--- a/Hand_edited_log/StudentsSolution.xlsx
+++ b/Hand_edited_log/StudentsSolution.xlsx
@@ -85,10 +85,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 17:45:16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 17:46:52</x:t>
+    <x:t>07-12-2025 18:01:25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 18:03:26</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>

--- a/Hand_edited_log/StudentsSolution.xlsx
+++ b/Hand_edited_log/StudentsSolution.xlsx
@@ -85,10 +85,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 18:01:25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 18:03:26</x:t>
+    <x:t>07-12-2025 18:40:45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 18:42:18</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>

--- a/Hand_edited_log/StudentsSolution.xlsx
+++ b/Hand_edited_log/StudentsSolution.xlsx
@@ -85,10 +85,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 18:40:45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 18:42:18</x:t>
+    <x:t>07-12-2025 19:21:44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 19:23:14</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>

--- a/Hand_edited_log/StudentsSolution.xlsx
+++ b/Hand_edited_log/StudentsSolution.xlsx
@@ -85,10 +85,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 19:21:44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 19:23:14</x:t>
+    <x:t>08-12-2025 01:07:20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 01:08:59</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>

--- a/Hand_edited_log/StudentsSolution.xlsx
+++ b/Hand_edited_log/StudentsSolution.xlsx
@@ -85,10 +85,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 01:07:20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08-12-2025 01:08:59</x:t>
+    <x:t>08-12-2025 01:29:12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 01:30:44</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>
